--- a/docs/testing/PROJECT TEST CASES CAA 301026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 301026.xlsx
@@ -10720,7 +10720,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>The hold is refused and the existing hold against EVT-1005 is identified. The calendar continues to show the period as Tentative for one event only</t>
+          <t>The hold is refused and the occupied buffered window is shown as unavailable, without naming EVT-1005 or its title (T-102). The calendar continues to show the period as Tentative for one event only</t>
         </is>
       </c>
     </row>
